--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R1325120032574f40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Raa4b3d82901c4386"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R5ddf63c64209479c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R84d1935444724994"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rd0227a6b3f6e4f88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R050b8ffcb8b248e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6c5ce5895c5d4f58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R8ee5dc964740421b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-07T00:43:44.962Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-07T08:19:57.914Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>ec066f78b134a4ab41e86b94133226ce6f6438520682c580b116eb56ed715fc9</x:v>
+        <x:v>682cddfb34b9ba0867e0152518ab5a1ad129de7bbb8828a58f64d23cf072cc71</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>99ba5edfb5f5ec7966456e3ad66285380fe1c91036b9f85ff7846b14c7fd32f2</x:v>
+        <x:v>4139f272a1dd534c1fd927881b22bba0c4b16ce3b4162f405c44d3aab380f491</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -2903,7 +2903,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b22ad45c2894e90"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6f7c96cf70345bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3213,7 +3213,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bf85e81e6e5417b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re80d222989e34e2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3322,7 +3322,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reed733c8a4e04843"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re300980d3376470e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rd0227a6b3f6e4f88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R050b8ffcb8b248e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6c5ce5895c5d4f58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R8ee5dc964740421b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R985949e0960b4ea3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R24d3db3563a94f57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rfc27f1f0ffdf4bb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R279b887c679f42a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-07T08:19:57.914Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-07T12:10:03.268Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>682cddfb34b9ba0867e0152518ab5a1ad129de7bbb8828a58f64d23cf072cc71</x:v>
+        <x:v>43d938ca7f8fb8bab04793528cf39b516a7cfa3e6f752cefca7203bfeafa0aac</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>4139f272a1dd534c1fd927881b22bba0c4b16ce3b4162f405c44d3aab380f491</x:v>
+        <x:v>a162fc27119841a75190b0bc0153cc17495a8bc432ad574a535e8a6799eb9a3d</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -2903,7 +2903,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6f7c96cf70345bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1edb8d3d0712411d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3213,7 +3213,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re80d222989e34e2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R485afac3b4f44dfa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3322,7 +3322,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re300980d3376470e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raae7159c02294b75"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R985949e0960b4ea3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R24d3db3563a94f57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rfc27f1f0ffdf4bb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R279b887c679f42a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R094e8bc030b547a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rcdaf166f99df4b61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rce84fbc138e14cf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R7a547b7567154b32"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-07T12:10:03.268Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-08T22:16:25.645Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>43d938ca7f8fb8bab04793528cf39b516a7cfa3e6f752cefca7203bfeafa0aac</x:v>
+        <x:v>53ff13ffefd2679cbf8d12a1e21bde566f40af08275ae4f0ff95823f70ea1b77</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>a162fc27119841a75190b0bc0153cc17495a8bc432ad574a535e8a6799eb9a3d</x:v>
+        <x:v>c883a38876b1d2b04788046ec5e1d87651113aa8dbfeb0f5415ba0b829f004ab</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -2903,7 +2903,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1edb8d3d0712411d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf324c9046c84e39"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3213,7 +3213,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R485afac3b4f44dfa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radda1ebd90884786"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3322,7 +3322,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raae7159c02294b75"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cacf798c2e54053"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R094e8bc030b547a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rcdaf166f99df4b61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rce84fbc138e14cf4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R7a547b7567154b32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R35615eb150d8435e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R8b97b239aeab49b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rbfd194be1dd8420a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rc21056fea09d4a24"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EquipmentRegister" displayName="EquipmentRegister" ref="A6:AC36" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EquipmentRegister" displayName="EquipmentRegister" ref="A6:AC40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="29">
     <x:tableColumn id="1" name="Equipment ID"/>
     <x:tableColumn id="2" name="Name"/>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-08T22:16:25.645Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-09T01:06:21.478Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -495,8 +495,8 @@
         <x:v>Current equipment</x:v>
       </x:c>
       <x:c r="B5" s="16" t="n">
-        <x:f>COUNTIFS(Equipment!$AA$7:$AA$36,"Current")</x:f>
-        <x:v>30</x:v>
+        <x:f>COUNTIFS(Equipment!$AA$7:$AA$40,"Current")</x:f>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
@@ -513,7 +513,7 @@
         <x:v>Retired equipment / routes</x:v>
       </x:c>
       <x:c r="B7" s="16" t="n">
-        <x:f>COUNTIFS(Equipment!$AA$7:$AA$36,"Retired")+COUNTIFS('Electrical Lines'!$Y$7:$Y$7,"Retired")</x:f>
+        <x:f>COUNTIFS(Equipment!$AA$7:$AA$40,"Retired")+COUNTIFS('Electrical Lines'!$Y$7:$Y$7,"Retired")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>53ff13ffefd2679cbf8d12a1e21bde566f40af08275ae4f0ff95823f70ea1b77</x:v>
+        <x:v>d4067e8bb027f3bb435cc6fee67c0fc1d0e462a2d8802a6ada0bb37df793ab52</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>c883a38876b1d2b04788046ec5e1d87651113aa8dbfeb0f5415ba0b829f004ab</x:v>
+        <x:v>e2130aeffb518d934149fa35c32d858856db06e804d9cb98aac4f1896cd3b761</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -2883,27 +2883,279 @@
         <x:v>{"length":7,"dim":1,"anchorY":7.2}</x:v>
       </x:c>
     </x:row>
+    <x:row r="37" ht="96" customHeight="1">
+      <x:c r="A37" s="8" t="str">
+        <x:v>D-WING-B-PETER</x:v>
+      </x:c>
+      <x:c r="B37" s="8" t="str">
+        <x:v>Saint Peter picture · wing B · concept</x:v>
+      </x:c>
+      <x:c r="C37" s="8" t="str">
+        <x:v>decor</x:v>
+      </x:c>
+      <x:c r="D37" s="8"/>
+      <x:c r="E37" s="8" t="str">
+        <x:v>DECOR</x:v>
+      </x:c>
+      <x:c r="F37" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="G37" s="11" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="H37" s="11" t="n">
+        <x:v>-13.095</x:v>
+      </x:c>
+      <x:c r="I37" s="8" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="J37" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K37" s="8" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="L37" s="8" t="str">
+        <x:v>See model parameters</x:v>
+      </x:c>
+      <x:c r="M37" s="8" t="str">
+        <x:v>Generated devotional concept. Frame proxy 1.12 × 1.62 m; actual size, material, glass, mounting and artwork approval pending. Unpowered.</x:v>
+      </x:c>
+      <x:c r="N37" s="11"/>
+      <x:c r="O37" s="11" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="P37" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q37" s="9"/>
+      <x:c r="R37" s="9"/>
+      <x:c r="S37" s="9"/>
+      <x:c r="T37" s="9"/>
+      <x:c r="U37" s="9"/>
+      <x:c r="V37" s="9"/>
+      <x:c r="W37" s="13"/>
+      <x:c r="X37" s="13"/>
+      <x:c r="Y37" s="13"/>
+      <x:c r="Z37" s="9"/>
+      <x:c r="AA37" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB37" s="8" t="str"/>
+      <x:c r="AC37" s="8" t="str">
+        <x:v>{"dim":1,"note":"USER CONFIRMED subjects/location: Peter and Paul between windows in each wing. CONCEPT 1.12 ×1.62 m frame proxy, Y2.20 centre. Actual size, height, substrate, frame, artwork and fixings pending. Unpow"}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="96" customHeight="1">
+      <x:c r="A38" s="8" t="str">
+        <x:v>D-WING-B-PAUL</x:v>
+      </x:c>
+      <x:c r="B38" s="8" t="str">
+        <x:v>Saint Paul picture · wing B · concept</x:v>
+      </x:c>
+      <x:c r="C38" s="8" t="str">
+        <x:v>decor</x:v>
+      </x:c>
+      <x:c r="D38" s="8"/>
+      <x:c r="E38" s="8" t="str">
+        <x:v>DECOR</x:v>
+      </x:c>
+      <x:c r="F38" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="G38" s="11" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="H38" s="11" t="n">
+        <x:v>-13.095</x:v>
+      </x:c>
+      <x:c r="I38" s="8" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="J38" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K38" s="8" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="L38" s="8" t="str">
+        <x:v>See model parameters</x:v>
+      </x:c>
+      <x:c r="M38" s="8" t="str">
+        <x:v>Generated devotional concept. Frame proxy 1.12 × 1.62 m; actual size, material, glass, mounting and artwork approval pending. Unpowered.</x:v>
+      </x:c>
+      <x:c r="N38" s="11"/>
+      <x:c r="O38" s="11" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="P38" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q38" s="9"/>
+      <x:c r="R38" s="9"/>
+      <x:c r="S38" s="9"/>
+      <x:c r="T38" s="9"/>
+      <x:c r="U38" s="9"/>
+      <x:c r="V38" s="9"/>
+      <x:c r="W38" s="13"/>
+      <x:c r="X38" s="13"/>
+      <x:c r="Y38" s="13"/>
+      <x:c r="Z38" s="9"/>
+      <x:c r="AA38" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB38" s="8" t="str"/>
+      <x:c r="AC38" s="8" t="str">
+        <x:v>{"dim":1,"note":"USER CONFIRMED subjects/location: Peter and Paul between windows in each wing. CONCEPT 1.12 ×1.62 m frame proxy, Y2.20 centre. Actual size, height, substrate, frame, artwork and fixings pending. Unpow"}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="96" customHeight="1">
+      <x:c r="A39" s="8" t="str">
+        <x:v>D-WING-H-PETER</x:v>
+      </x:c>
+      <x:c r="B39" s="8" t="str">
+        <x:v>Saint Peter picture · wing H · concept</x:v>
+      </x:c>
+      <x:c r="C39" s="8" t="str">
+        <x:v>decor</x:v>
+      </x:c>
+      <x:c r="D39" s="8"/>
+      <x:c r="E39" s="8" t="str">
+        <x:v>DECOR</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="n">
+        <x:v>39.7</x:v>
+      </x:c>
+      <x:c r="G39" s="11" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="H39" s="11" t="n">
+        <x:v>13.095</x:v>
+      </x:c>
+      <x:c r="I39" s="8" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="J39" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K39" s="8" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="L39" s="8" t="str">
+        <x:v>See model parameters</x:v>
+      </x:c>
+      <x:c r="M39" s="8" t="str">
+        <x:v>Generated devotional concept. Frame proxy 1.12 × 1.62 m; actual size, material, glass, mounting and artwork approval pending. Unpowered.</x:v>
+      </x:c>
+      <x:c r="N39" s="11"/>
+      <x:c r="O39" s="11" t="n">
+        <x:v>-90</x:v>
+      </x:c>
+      <x:c r="P39" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q39" s="9"/>
+      <x:c r="R39" s="9"/>
+      <x:c r="S39" s="9"/>
+      <x:c r="T39" s="9"/>
+      <x:c r="U39" s="9"/>
+      <x:c r="V39" s="9"/>
+      <x:c r="W39" s="13"/>
+      <x:c r="X39" s="13"/>
+      <x:c r="Y39" s="13"/>
+      <x:c r="Z39" s="9"/>
+      <x:c r="AA39" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB39" s="8" t="str"/>
+      <x:c r="AC39" s="8" t="str">
+        <x:v>{"dim":1,"note":"USER CONFIRMED subjects/location: Peter and Paul between windows in each wing. CONCEPT 1.12 ×1.62 m frame proxy, Y2.20 centre. Actual size, height, substrate, frame, artwork and fixings pending. Unpow"}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="96" customHeight="1">
+      <x:c r="A40" s="8" t="str">
+        <x:v>D-WING-H-PAUL</x:v>
+      </x:c>
+      <x:c r="B40" s="8" t="str">
+        <x:v>Saint Paul picture · wing H · concept</x:v>
+      </x:c>
+      <x:c r="C40" s="8" t="str">
+        <x:v>decor</x:v>
+      </x:c>
+      <x:c r="D40" s="8"/>
+      <x:c r="E40" s="8" t="str">
+        <x:v>DECOR</x:v>
+      </x:c>
+      <x:c r="F40" s="11" t="n">
+        <x:v>41.45</x:v>
+      </x:c>
+      <x:c r="G40" s="11" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="H40" s="11" t="n">
+        <x:v>13.095</x:v>
+      </x:c>
+      <x:c r="I40" s="8" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="J40" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K40" s="8" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="L40" s="8" t="str">
+        <x:v>See model parameters</x:v>
+      </x:c>
+      <x:c r="M40" s="8" t="str">
+        <x:v>Generated devotional concept. Frame proxy 1.12 × 1.62 m; actual size, material, glass, mounting and artwork approval pending. Unpowered.</x:v>
+      </x:c>
+      <x:c r="N40" s="11"/>
+      <x:c r="O40" s="11" t="n">
+        <x:v>-90</x:v>
+      </x:c>
+      <x:c r="P40" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q40" s="9"/>
+      <x:c r="R40" s="9"/>
+      <x:c r="S40" s="9"/>
+      <x:c r="T40" s="9"/>
+      <x:c r="U40" s="9"/>
+      <x:c r="V40" s="9"/>
+      <x:c r="W40" s="13"/>
+      <x:c r="X40" s="13"/>
+      <x:c r="Y40" s="13"/>
+      <x:c r="Z40" s="9"/>
+      <x:c r="AA40" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB40" s="8" t="str"/>
+      <x:c r="AC40" s="8" t="str">
+        <x:v>{"dim":1,"note":"USER CONFIRMED subjects/location: Peter and Paul between windows in each wing. CONCEPT 1.12 ×1.62 m frame proxy, Y2.20 centre. Actual size, height, substrate, frame, artwork and fixings pending. Unpow"}</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="AA7:AA36">
+  <x:conditionalFormatting sqref="AA7:AA40">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
-    <x:dataValidation type="decimal" operator="between" sqref="W7:W36">
+    <x:dataValidation type="decimal" operator="between" sqref="W7:W40">
       <x:formula1>-1000</x:formula1>
       <x:formula2>1000</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="between" sqref="X7:X36">
+    <x:dataValidation type="decimal" operator="between" sqref="X7:X40">
       <x:formula1>-1000</x:formula1>
       <x:formula2>1000</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="between" sqref="Y7:Y36">
+    <x:dataValidation type="decimal" operator="between" sqref="Y7:Y40">
       <x:formula1>-1000</x:formula1>
       <x:formula2>1000</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf324c9046c84e39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra81635adc66140af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3213,7 +3465,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radda1ebd90884786"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde283124f7874db6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3322,7 +3574,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cacf798c2e54053"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re51f6c0f4faf4296"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R35615eb150d8435e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R8b97b239aeab49b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rbfd194be1dd8420a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rc21056fea09d4a24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R834c36e149d44e90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R9c5b0d61629d4835"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R3bca83c126f14188"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R964eacbf2c9640eb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-09T01:06:21.478Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-09T01:31:17.233Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>d4067e8bb027f3bb435cc6fee67c0fc1d0e462a2d8802a6ada0bb37df793ab52</x:v>
+        <x:v>80b0da7d5afe7ebc6ad40230d4100ad0f2b4b395a8a63b44da5d741ccd64e05d</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>e2130aeffb518d934149fa35c32d858856db06e804d9cb98aac4f1896cd3b761</x:v>
+        <x:v>78a1f21a5458fc451b1fadb227a547feb6afa62226cd02a3db53eaacd4fe65ce</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3155,7 +3155,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra81635adc66140af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf98e7e4b02cf4caa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3465,7 +3465,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde283124f7874db6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R081d7be2ab8b40ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3574,7 +3574,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re51f6c0f4faf4296"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9c312a6218841da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R834c36e149d44e90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R9c5b0d61629d4835"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R3bca83c126f14188"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R964eacbf2c9640eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R007307d2df7e414e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rdec00c77a8904749"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R63d67c76cb884597"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R73d3872ebf714ba0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EquipmentRegister" displayName="EquipmentRegister" ref="A6:AC40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EquipmentRegister" displayName="EquipmentRegister" ref="A6:AC43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="29">
     <x:tableColumn id="1" name="Equipment ID"/>
     <x:tableColumn id="2" name="Name"/>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-09T01:31:17.233Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-09T03:17:36.119Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -495,8 +495,8 @@
         <x:v>Current equipment</x:v>
       </x:c>
       <x:c r="B5" s="16" t="n">
-        <x:f>COUNTIFS(Equipment!$AA$7:$AA$40,"Current")</x:f>
-        <x:v>34</x:v>
+        <x:f>COUNTIFS(Equipment!$AA$7:$AA$43,"Current")</x:f>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
@@ -513,7 +513,7 @@
         <x:v>Retired equipment / routes</x:v>
       </x:c>
       <x:c r="B7" s="16" t="n">
-        <x:f>COUNTIFS(Equipment!$AA$7:$AA$40,"Retired")+COUNTIFS('Electrical Lines'!$Y$7:$Y$7,"Retired")</x:f>
+        <x:f>COUNTIFS(Equipment!$AA$7:$AA$43,"Retired")+COUNTIFS('Electrical Lines'!$Y$7:$Y$7,"Retired")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>80b0da7d5afe7ebc6ad40230d4100ad0f2b4b395a8a63b44da5d741ccd64e05d</x:v>
+        <x:v>f58ecb8c7e66db5f5a9c359a0501f9a7ff3253b9cb9664b76918bdc2f036e05a</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>78a1f21a5458fc451b1fadb227a547feb6afa62226cd02a3db53eaacd4fe65ce</x:v>
+        <x:v>1646f19d4f8b80070625f5fb407f54d11abbea5d7ecb7c88a4a2534f18542306</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3135,27 +3135,216 @@
         <x:v>{"dim":1,"note":"USER CONFIRMED subjects/location: Peter and Paul between windows in each wing. CONCEPT 1.12 ×1.62 m frame proxy, Y2.20 centre. Actual size, height, substrate, frame, artwork and fixings pending. Unpow"}</x:v>
       </x:c>
     </x:row>
+    <x:row r="41" ht="96" customHeight="1">
+      <x:c r="A41" s="8" t="str">
+        <x:v>D-FACADE-C</x:v>
+      </x:c>
+      <x:c r="B41" s="8" t="str">
+        <x:v>Façade statue · Assumption of Our Lady</x:v>
+      </x:c>
+      <x:c r="C41" s="8" t="str">
+        <x:v>decor</x:v>
+      </x:c>
+      <x:c r="D41" s="8"/>
+      <x:c r="E41" s="8" t="str">
+        <x:v>DECOR</x:v>
+      </x:c>
+      <x:c r="F41" s="11" t="n">
+        <x:v>2.29</x:v>
+      </x:c>
+      <x:c r="G41" s="11" t="n">
+        <x:v>11.8</x:v>
+      </x:c>
+      <x:c r="H41" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I41" s="8" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="J41" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K41" s="8" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="L41" s="8" t="str">
+        <x:v>See model parameters</x:v>
+      </x:c>
+      <x:c r="M41" s="8" t="str">
+        <x:v>Ivory figure 2.2 m on a cloud plinth, open raised arms and upturned face, for the central façade niche. Generated concept: the sculptor, size, material, weight and fixing are pending.</x:v>
+      </x:c>
+      <x:c r="N41" s="11"/>
+      <x:c r="O41" s="11" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="P41" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q41" s="9"/>
+      <x:c r="R41" s="9"/>
+      <x:c r="S41" s="9"/>
+      <x:c r="T41" s="9"/>
+      <x:c r="U41" s="9"/>
+      <x:c r="V41" s="9"/>
+      <x:c r="W41" s="13"/>
+      <x:c r="X41" s="13"/>
+      <x:c r="Y41" s="13"/>
+      <x:c r="Z41" s="9"/>
+      <x:c r="AA41" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB41" s="8" t="str"/>
+      <x:c r="AC41" s="8" t="str">
+        <x:v>{"dim":1,"note":"USER CONFIRMED subject and place. Generated figure on the drawn niche pedestal. Sculptor, size, material, weight and fixing pending."}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="96" customHeight="1">
+      <x:c r="A42" s="8" t="str">
+        <x:v>D-FACADE-B</x:v>
+      </x:c>
+      <x:c r="B42" s="8" t="str">
+        <x:v>Façade statue · Saint Peter</x:v>
+      </x:c>
+      <x:c r="C42" s="8" t="str">
+        <x:v>decor</x:v>
+      </x:c>
+      <x:c r="D42" s="8"/>
+      <x:c r="E42" s="8" t="str">
+        <x:v>DECOR</x:v>
+      </x:c>
+      <x:c r="F42" s="11" t="n">
+        <x:v>2.29</x:v>
+      </x:c>
+      <x:c r="G42" s="11" t="n">
+        <x:v>10.08</x:v>
+      </x:c>
+      <x:c r="H42" s="11" t="n">
+        <x:v>-5.48</x:v>
+      </x:c>
+      <x:c r="I42" s="8" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="J42" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K42" s="8" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="L42" s="8" t="str">
+        <x:v>See model parameters</x:v>
+      </x:c>
+      <x:c r="M42" s="8" t="str">
+        <x:v>Ivory figure 1.78 m with keys and book, for a side façade niche. Generated concept: subject, sculptor, size, material, weight and fixing are pending.</x:v>
+      </x:c>
+      <x:c r="N42" s="11"/>
+      <x:c r="O42" s="11" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="P42" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q42" s="9"/>
+      <x:c r="R42" s="9"/>
+      <x:c r="S42" s="9"/>
+      <x:c r="T42" s="9"/>
+      <x:c r="U42" s="9"/>
+      <x:c r="V42" s="9"/>
+      <x:c r="W42" s="13"/>
+      <x:c r="X42" s="13"/>
+      <x:c r="Y42" s="13"/>
+      <x:c r="Z42" s="9"/>
+      <x:c r="AA42" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB42" s="8" t="str"/>
+      <x:c r="AC42" s="8" t="str">
+        <x:v>{"dim":1,"note":"PROPOSED subject; owner to confirm the two saints. Generated figure on the drawn niche pedestal. Sculptor, size, material, weight and fixing pending."}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="96" customHeight="1">
+      <x:c r="A43" s="8" t="str">
+        <x:v>D-FACADE-H</x:v>
+      </x:c>
+      <x:c r="B43" s="8" t="str">
+        <x:v>Façade statue · Saint Paul</x:v>
+      </x:c>
+      <x:c r="C43" s="8" t="str">
+        <x:v>decor</x:v>
+      </x:c>
+      <x:c r="D43" s="8"/>
+      <x:c r="E43" s="8" t="str">
+        <x:v>DECOR</x:v>
+      </x:c>
+      <x:c r="F43" s="11" t="n">
+        <x:v>2.29</x:v>
+      </x:c>
+      <x:c r="G43" s="11" t="n">
+        <x:v>10.08</x:v>
+      </x:c>
+      <x:c r="H43" s="11" t="n">
+        <x:v>5.48</x:v>
+      </x:c>
+      <x:c r="I43" s="8" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="J43" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K43" s="8" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="L43" s="8" t="str">
+        <x:v>See model parameters</x:v>
+      </x:c>
+      <x:c r="M43" s="8" t="str">
+        <x:v>Ivory figure 1.78 m with sword and book, for a side façade niche. Generated concept: subject, sculptor, size, material, weight and fixing are pending.</x:v>
+      </x:c>
+      <x:c r="N43" s="11"/>
+      <x:c r="O43" s="11" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="P43" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q43" s="9"/>
+      <x:c r="R43" s="9"/>
+      <x:c r="S43" s="9"/>
+      <x:c r="T43" s="9"/>
+      <x:c r="U43" s="9"/>
+      <x:c r="V43" s="9"/>
+      <x:c r="W43" s="13"/>
+      <x:c r="X43" s="13"/>
+      <x:c r="Y43" s="13"/>
+      <x:c r="Z43" s="9"/>
+      <x:c r="AA43" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB43" s="8" t="str"/>
+      <x:c r="AC43" s="8" t="str">
+        <x:v>{"dim":1,"note":"PROPOSED subject; owner to confirm the two saints. Generated figure on the drawn niche pedestal. Sculptor, size, material, weight and fixing pending."}</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="AA7:AA40">
+  <x:conditionalFormatting sqref="AA7:AA43">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
-    <x:dataValidation type="decimal" operator="between" sqref="W7:W40">
+    <x:dataValidation type="decimal" operator="between" sqref="W7:W43">
       <x:formula1>-1000</x:formula1>
       <x:formula2>1000</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="between" sqref="X7:X40">
+    <x:dataValidation type="decimal" operator="between" sqref="X7:X43">
       <x:formula1>-1000</x:formula1>
       <x:formula2>1000</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="between" sqref="Y7:Y40">
+    <x:dataValidation type="decimal" operator="between" sqref="Y7:Y43">
       <x:formula1>-1000</x:formula1>
       <x:formula2>1000</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf98e7e4b02cf4caa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fe4addaf1ca43e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3465,7 +3654,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R081d7be2ab8b40ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61b606a3cc1c403e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3574,7 +3763,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9c312a6218841da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92f0b63feed94e4c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R007307d2df7e414e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rdec00c77a8904749"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R63d67c76cb884597"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R73d3872ebf714ba0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rd0fcfa161c7a4625"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re9d78a6c27b348b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Re27920c833ec459a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R1acafda8db394e0a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-09T03:17:36.119Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-09T04:54:03.663Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>f58ecb8c7e66db5f5a9c359a0501f9a7ff3253b9cb9664b76918bdc2f036e05a</x:v>
+        <x:v>e8b0d45e0c5518ca0cc64c1fa511adc8ba03ba31bef6d46426ff3c0c3e699bab</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>1646f19d4f8b80070625f5fb407f54d11abbea5d7ecb7c88a4a2534f18542306</x:v>
+        <x:v>e25c59374b1948a67cdb0ee5bed0beb9884da65931cb92b8dc2af738d4ae1e28</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3344,7 +3344,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fe4addaf1ca43e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75911d1e3c024113"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3654,7 +3654,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61b606a3cc1c403e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f7649c8e17a489a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3763,7 +3763,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92f0b63feed94e4c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fbcf4d80a544d29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rd0fcfa161c7a4625"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re9d78a6c27b348b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Re27920c833ec459a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R1acafda8db394e0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R77e1ac7a06a543d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R334d68277e054d2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rf44f09af745c4796"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rb856aa98d2e14b8a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-09T04:54:03.663Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-09T06:49:14.923Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>e8b0d45e0c5518ca0cc64c1fa511adc8ba03ba31bef6d46426ff3c0c3e699bab</x:v>
+        <x:v>0a6cf2aa5294b46ad1ca267ef78dada74d793fdb4a83f39e392746594b74ba7c</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -3344,7 +3344,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75911d1e3c024113"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1eafc3b23434128"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3654,7 +3654,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f7649c8e17a489a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cbcaf81d616438a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3763,7 +3763,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fbcf4d80a544d29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbc42d3b2db44f06"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R77e1ac7a06a543d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R334d68277e054d2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rf44f09af745c4796"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rb856aa98d2e14b8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R8d21d901577440e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rce3e41e66d984ee4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rd1f3111d3e1a495c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R0156fe1c265549bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -77,7 +77,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -487,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-09T06:49:14.923Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-17T21:08:50.163Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>0a6cf2aa5294b46ad1ca267ef78dada74d793fdb4a83f39e392746594b74ba7c</x:v>
+        <x:v>37e3acfbe7b2353ccb6bf951d166ae573b85d990a0e3cb06b573b995c64fefa8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>e25c59374b1948a67cdb0ee5bed0beb9884da65931cb92b8dc2af738d4ae1e28</x:v>
+        <x:v>dbabc0c9ddcd7207edad13de9e8b20f5da0865700167c5f9fe7c34d6d03b22b4</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3344,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1eafc3b23434128"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddd612e021114196"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3654,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cbcaf81d616438a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3bc19776cf64863"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3763,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbc42d3b2db44f06"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8172f32973f141fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R8d21d901577440e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rce3e41e66d984ee4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rd1f3111d3e1a495c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R0156fe1c265549bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R840bb9e2b749481c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R5e40a7b20ae14a65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R802c49ab65f449a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R9e71b47183094505"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-17T21:08:50.163Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-17T21:33:54.811Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>37e3acfbe7b2353ccb6bf951d166ae573b85d990a0e3cb06b573b995c64fefa8</x:v>
+        <x:v>40c0fb48adb616822d2737a378024e64d46f211fcc43ca75ea298cd2570965f8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>dbabc0c9ddcd7207edad13de9e8b20f5da0865700167c5f9fe7c34d6d03b22b4</x:v>
+        <x:v>e8507810679907dc3354f9387ce0b6d5f3b3e307d5939a52680f19a914a4cd86</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddd612e021114196"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd57ee3724554818"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3bc19776cf64863"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82b74237e76d4cdf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8172f32973f141fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree100367b0254e88"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R840bb9e2b749481c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R5e40a7b20ae14a65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R802c49ab65f449a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R9e71b47183094505"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R78c08e2b22f34f96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rc3820dc4c5464683"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R80890960a78f4e39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rf09724408c5a44b0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-17T21:33:54.811Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-19T08:15:40.780Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>40c0fb48adb616822d2737a378024e64d46f211fcc43ca75ea298cd2570965f8</x:v>
+        <x:v>377a9614312a02f792043db75f19539177eac31dbb6fbce22ffc70cc36f6d6f9</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>e8507810679907dc3354f9387ce0b6d5f3b3e307d5939a52680f19a914a4cd86</x:v>
+        <x:v>7407c92e37c8f0d1299afa3b00360d1b00fbe1db0f067d0666f57047093f1960</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd57ee3724554818"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8904e873c3324b0c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82b74237e76d4cdf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00616556fe53435f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree100367b0254e88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb68ac9bcc7ba4e91"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R78c08e2b22f34f96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rc3820dc4c5464683"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R80890960a78f4e39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rf09724408c5a44b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R612f2d051bac45f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R2d19dda1b74f4321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R9ef5ff1bf065483b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R23132cedf51e4a9a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-19T08:15:40.780Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-19T08:50:48.752Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>377a9614312a02f792043db75f19539177eac31dbb6fbce22ffc70cc36f6d6f9</x:v>
+        <x:v>5f987e29647ab0b5cedad770eae700cb80b204e95ea85d8a400edb95c4d1128d</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8904e873c3324b0c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84425c07c8e042be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00616556fe53435f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc2a512bc0a14f94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb68ac9bcc7ba4e91"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d4b15427c1d4424"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R612f2d051bac45f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R2d19dda1b74f4321"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R9ef5ff1bf065483b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R23132cedf51e4a9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R6202422b4ce549b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R93951b2ae6764747"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc7dec8b511154c2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rf36f69c01dbc4fa0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-19T08:50:48.752Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-19T11:17:33.830Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5f987e29647ab0b5cedad770eae700cb80b204e95ea85d8a400edb95c4d1128d</x:v>
+        <x:v>76909d79225afb700a61e3530abc09d363cc6e053b648e6ff87757a6c3bc33f9</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>7407c92e37c8f0d1299afa3b00360d1b00fbe1db0f067d0666f57047093f1960</x:v>
+        <x:v>5c2b7909fdbf3eab73054e0a16a6cfe55decd4f3c81b9a88867863ffd7c0fef1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84425c07c8e042be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9d72a6e34034f62"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc2a512bc0a14f94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71682b310d3a454e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d4b15427c1d4424"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf372fce3b0ea42da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R6202422b4ce549b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R93951b2ae6764747"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc7dec8b511154c2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rf36f69c01dbc4fa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Ra264e52ebb274647"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R3bb1924b57834407"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R376289f155044c91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R9b40ed2823cb44b4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-19T11:17:33.830Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-19T13:14:34.808Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>76909d79225afb700a61e3530abc09d363cc6e053b648e6ff87757a6c3bc33f9</x:v>
+        <x:v>5e78147eff2f4a61ae97936ba8b51920b75ba77bd982e40a1cae0206f908332c</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>5c2b7909fdbf3eab73054e0a16a6cfe55decd4f3c81b9a88867863ffd7c0fef1</x:v>
+        <x:v>7a659950a4bf89cc57551f6d9714dbafa89ad76ea9820ddefb4bbc73056b5b2e</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9d72a6e34034f62"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bae42d9d714422f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71682b310d3a454e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9698146da4bf46fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf372fce3b0ea42da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2835c353931a4d53"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Ra264e52ebb274647"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R3bb1924b57834407"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R376289f155044c91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R9b40ed2823cb44b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rce2f3ec0cbb94526"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rf7543572c75f4d07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R0f8a295f89d241a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Ra12aec1e18754415"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-19T13:14:34.808Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-23T23:29:38.571Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5e78147eff2f4a61ae97936ba8b51920b75ba77bd982e40a1cae0206f908332c</x:v>
+        <x:v>19eb3af4e9e190d44f45651a83746b308f3bc351650fff669ae77f5ce0cb3e9d</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>7a659950a4bf89cc57551f6d9714dbafa89ad76ea9820ddefb4bbc73056b5b2e</x:v>
+        <x:v>ec7eed586921cecf1c820f16f5ebefd971b44f66cd4eae78e00a7540b47ad9d9</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1099,7 +1099,7 @@
         <x:v>47.2</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>0.75</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="H9" s="11" t="n">
         <x:v>-1.15</x:v>
@@ -1162,7 +1162,7 @@
         <x:v>45.15</x:v>
       </x:c>
       <x:c r="G10" s="11" t="n">
-        <x:v>0.75</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="H10" s="11" t="n">
         <x:v>-2.9</x:v>
@@ -1477,7 +1477,7 @@
         <x:v>47.2</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>0.75</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="H15" s="11" t="n">
         <x:v>1.15</x:v>
@@ -1540,7 +1540,7 @@
         <x:v>45.15</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>0.75</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
         <x:v>2.9</x:v>
@@ -1855,7 +1855,7 @@
         <x:v>40.769999999999996</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
-        <x:v>0.75</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
         <x:v>-1.55</x:v>
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bae42d9d714422f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb20e25c1854b4b5b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9698146da4bf46fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53a3c044fa0c474f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2835c353931a4d53"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2994b71db1cf4113"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rce2f3ec0cbb94526"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rf7543572c75f4d07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R0f8a295f89d241a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Ra12aec1e18754415"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rc1e6535ee6aa4697"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R8571023b2dca4e16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R0f8a146d12594f43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rd27ecca0daab4e67"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-23T23:29:38.571Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T00:39:01.684Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>19eb3af4e9e190d44f45651a83746b308f3bc351650fff669ae77f5ce0cb3e9d</x:v>
+        <x:v>146da28a773b5232adb7a991941b4c52312ffa1c721c3656a3930b7eeac1bb23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>ec7eed586921cecf1c820f16f5ebefd971b44f66cd4eae78e00a7540b47ad9d9</x:v>
+        <x:v>c2461516b6454aa96dec6678dad1bc8b977620d5c08160037ef8b86f7f230532</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3156,10 +3156,10 @@
         <x:v>DECOR</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
-        <x:v>2.29</x:v>
+        <x:v>4.08</x:v>
       </x:c>
       <x:c r="G41" s="11" t="n">
-        <x:v>11.8</x:v>
+        <x:v>16.683</x:v>
       </x:c>
       <x:c r="H41" s="11" t="n">
         <x:v>0</x:v>
@@ -3219,13 +3219,13 @@
         <x:v>DECOR</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
-        <x:v>2.29</x:v>
+        <x:v>4.15</x:v>
       </x:c>
       <x:c r="G42" s="11" t="n">
-        <x:v>10.08</x:v>
+        <x:v>10.391</x:v>
       </x:c>
       <x:c r="H42" s="11" t="n">
-        <x:v>-5.48</x:v>
+        <x:v>-5.35</x:v>
       </x:c>
       <x:c r="I42" s="8" t="str">
         <x:v>floor</x:v>
@@ -3282,13 +3282,13 @@
         <x:v>DECOR</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:v>2.29</x:v>
+        <x:v>4.15</x:v>
       </x:c>
       <x:c r="G43" s="11" t="n">
-        <x:v>10.08</x:v>
+        <x:v>10.391</x:v>
       </x:c>
       <x:c r="H43" s="11" t="n">
-        <x:v>5.48</x:v>
+        <x:v>5.35</x:v>
       </x:c>
       <x:c r="I43" s="8" t="str">
         <x:v>floor</x:v>
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb20e25c1854b4b5b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red547a85dacf4df9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53a3c044fa0c474f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4ac8af5b07a4b45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2994b71db1cf4113"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R213e79310a694767"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rc1e6535ee6aa4697"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R8571023b2dca4e16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R0f8a146d12594f43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rd27ecca0daab4e67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rcf5253959b754e88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R06fd38912870463a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R2996f28a41b1494e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Racafad2265554a4b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T00:39:01.684Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T16:03:51.012Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>146da28a773b5232adb7a991941b4c52312ffa1c721c3656a3930b7eeac1bb23</x:v>
+        <x:v>5426ce45cb04f814d5dd0210f8e96b572936a920fad8790c50d7c5cfa6b6676e</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>c2461516b6454aa96dec6678dad1bc8b977620d5c08160037ef8b86f7f230532</x:v>
+        <x:v>b17314130617491f3e73a772bab5720c8ffe36baa24ed5a5cc2512f8640338ef</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -970,7 +970,7 @@
         <x:v>DECOR</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>44.275</x:v>
+        <x:v>48.83</x:v>
       </x:c>
       <x:c r="G7" s="11" t="n">
         <x:v>2.85</x:v>
@@ -1033,7 +1033,7 @@
         <x:v>DECOR</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>44.275</x:v>
+        <x:v>48.83</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
         <x:v>2.85</x:v>
@@ -1222,7 +1222,7 @@
         <x:v>DECOR</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>44.225</x:v>
+        <x:v>48.78</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
         <x:v>2.85</x:v>
@@ -1285,7 +1285,7 @@
         <x:v>DECOR</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
-        <x:v>44.225</x:v>
+        <x:v>48.78</x:v>
       </x:c>
       <x:c r="G12" s="11" t="n">
         <x:v>2.85</x:v>
@@ -1600,7 +1600,7 @@
         <x:v>DECOR</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>44.225</x:v>
+        <x:v>48.78</x:v>
       </x:c>
       <x:c r="G17" s="11" t="n">
         <x:v>2.85</x:v>
@@ -1663,7 +1663,7 @@
         <x:v>DECOR</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>44.225</x:v>
+        <x:v>48.78</x:v>
       </x:c>
       <x:c r="G18" s="11" t="n">
         <x:v>2.85</x:v>
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red547a85dacf4df9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R534e1377823545f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4ac8af5b07a4b45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c1a3e13ad25450b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R213e79310a694767"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R390cd8a091ec4582"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rcf5253959b754e88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R06fd38912870463a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R2996f28a41b1494e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Racafad2265554a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R763468e1dcd44963"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rc012044a44ee472e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R37a79ac0ad8f4dec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R0acad62557e14d22"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T16:03:51.012Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T16:44:17.712Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5426ce45cb04f814d5dd0210f8e96b572936a920fad8790c50d7c5cfa6b6676e</x:v>
+        <x:v>c5d56493e89032b01436ecaed120866a09d5872d997065e2e10f3c09d0d21e41</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>b17314130617491f3e73a772bab5720c8ffe36baa24ed5a5cc2512f8640338ef</x:v>
+        <x:v>10d6d18e117107f62a3d3e48f08d9f8d9df9954b8ce3c3d85d06553452833a75</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -2228,7 +2228,7 @@
       </x:c>
       <x:c r="AB26" s="8" t="str"/>
       <x:c r="AC26" s="8" t="str">
-        <x:v>{"length":3.4,"dim":1,"anchorY":6.798875000000001}</x:v>
+        <x:v>{"length":3.4,"dim":1,"anchorY":6.638660220994475}</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="96" customHeight="1">
@@ -2295,7 +2295,7 @@
       </x:c>
       <x:c r="AB27" s="8" t="str"/>
       <x:c r="AC27" s="8" t="str">
-        <x:v>{"length":3.4,"dim":1,"anchorY":6.798875000000001}</x:v>
+        <x:v>{"length":3.4,"dim":1,"anchorY":6.638660220994475}</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="96" customHeight="1">
@@ -2362,7 +2362,7 @@
       </x:c>
       <x:c r="AB28" s="8" t="str"/>
       <x:c r="AC28" s="8" t="str">
-        <x:v>{"length":3.4,"dim":1,"anchorY":6.798875000000001}</x:v>
+        <x:v>{"length":3.4,"dim":1,"anchorY":6.638660220994475}</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="96" customHeight="1">
@@ -2429,7 +2429,7 @@
       </x:c>
       <x:c r="AB29" s="8" t="str"/>
       <x:c r="AC29" s="8" t="str">
-        <x:v>{"length":3.4,"dim":1,"anchorY":6.798875000000001}</x:v>
+        <x:v>{"length":3.4,"dim":1,"anchorY":6.638660220994475}</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="96" customHeight="1">
@@ -2496,7 +2496,7 @@
       </x:c>
       <x:c r="AB30" s="8" t="str"/>
       <x:c r="AC30" s="8" t="str">
-        <x:v>{"length":3.4,"dim":1,"anchorY":6.798875000000001}</x:v>
+        <x:v>{"length":3.4,"dim":1,"anchorY":6.638660220994475}</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="96" customHeight="1">
@@ -2563,7 +2563,7 @@
       </x:c>
       <x:c r="AB31" s="8" t="str"/>
       <x:c r="AC31" s="8" t="str">
-        <x:v>{"length":3.4,"dim":1,"anchorY":6.798875000000001}</x:v>
+        <x:v>{"length":3.4,"dim":1,"anchorY":6.638660220994475}</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="96" customHeight="1">
@@ -2630,7 +2630,7 @@
       </x:c>
       <x:c r="AB32" s="8" t="str"/>
       <x:c r="AC32" s="8" t="str">
-        <x:v>{"length":3.4,"dim":1,"anchorY":6.798875000000001}</x:v>
+        <x:v>{"length":3.4,"dim":1,"anchorY":6.638660220994475}</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="96" customHeight="1">
@@ -2697,7 +2697,7 @@
       </x:c>
       <x:c r="AB33" s="8" t="str"/>
       <x:c r="AC33" s="8" t="str">
-        <x:v>{"length":3.4,"dim":1,"anchorY":6.798875000000001}</x:v>
+        <x:v>{"length":3.4,"dim":1,"anchorY":6.638660220994475}</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="96" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R534e1377823545f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde67fdc6754b4adf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c1a3e13ad25450b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05d31b5a2da44636"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R390cd8a091ec4582"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e32790390384029"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R763468e1dcd44963"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rc012044a44ee472e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R37a79ac0ad8f4dec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R0acad62557e14d22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R0ad9ba00a5ec4744"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R7f939816f0f94266"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R5ed471c4640d49a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Ref0f788e9a83444b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T16:44:17.712Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T17:01:56.972Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>c5d56493e89032b01436ecaed120866a09d5872d997065e2e10f3c09d0d21e41</x:v>
+        <x:v>13047932f1698050c4ec862686991828799970abdcdf394a64d82404d1fcbee8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>10d6d18e117107f62a3d3e48f08d9f8d9df9954b8ce3c3d85d06553452833a75</x:v>
+        <x:v>2faac8500a07543b677dc990e5aad2b96fa69acb639f440c57dab2001fa28053</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde67fdc6754b4adf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe2459ba0ca14174"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05d31b5a2da44636"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb601c68cc3e44919"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e32790390384029"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b6fd31fbc174933"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R0ad9ba00a5ec4744"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R7f939816f0f94266"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R5ed471c4640d49a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Ref0f788e9a83444b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R6cdf0b79070f40a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb6a5d43de9974510"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rdea380f7934b4071"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Ra56e6a7a98794910"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T17:01:56.972Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T17:09:33.226Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>13047932f1698050c4ec862686991828799970abdcdf394a64d82404d1fcbee8</x:v>
+        <x:v>8494709266c989cc26ec0f16481a494804ce05b0210fea7ddf78e6004c0e1614</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>2faac8500a07543b677dc990e5aad2b96fa69acb639f440c57dab2001fa28053</x:v>
+        <x:v>760fbab99b5e7a6f8a94c497e4a9254bf06be7fb81bd104e0e2b4126c9fde701</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe2459ba0ca14174"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb22032d88c0d4328"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb601c68cc3e44919"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb5dcf883d304fe0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b6fd31fbc174933"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf33586d648b14375"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R6cdf0b79070f40a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb6a5d43de9974510"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rdea380f7934b4071"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Ra56e6a7a98794910"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rac18dfa1f15e4f77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R0b202a48d40c449c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Ra7e70a1f64014ffe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R433a91310b8a4ed6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T17:09:33.226Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T17:42:22.582Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>8494709266c989cc26ec0f16481a494804ce05b0210fea7ddf78e6004c0e1614</x:v>
+        <x:v>94f37cc477b452b68afd0631937580a0b9412b859965e9046c49f59c64746a3f</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>760fbab99b5e7a6f8a94c497e4a9254bf06be7fb81bd104e0e2b4126c9fde701</x:v>
+        <x:v>1c162288ea3d9215a1f3a3feb59b009079a72c6a8a777f9f9044923d3b18ad31</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb22032d88c0d4328"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3a7474a2de2434d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb5dcf883d304fe0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5ac94bfe359475c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf33586d648b14375"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra42339e5dd0b4324"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rac18dfa1f15e4f77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R0b202a48d40c449c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Ra7e70a1f64014ffe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R433a91310b8a4ed6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rb9d299af7e57431c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R4922920085504f22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Ra37da7f755ec4cb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R550c50c837e04ac7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T17:42:22.582Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T17:49:59.196Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>94f37cc477b452b68afd0631937580a0b9412b859965e9046c49f59c64746a3f</x:v>
+        <x:v>88062f7a6e23d78621ee2f69e0c94047babf12437db78098dd47d3bedd6e18e8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>1c162288ea3d9215a1f3a3feb59b009079a72c6a8a777f9f9044923d3b18ad31</x:v>
+        <x:v>fb798ccf47bd62d17275121a5ca1021b3ed9a80358d236bd57d75a7be070b894</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3a7474a2de2434d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6aa021399ce74992"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5ac94bfe359475c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d292687eb104057"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra42339e5dd0b4324"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde0b57c891514689"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rb9d299af7e57431c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R4922920085504f22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Ra37da7f755ec4cb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R550c50c837e04ac7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rae3ebd355d6d45fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R99963fb4a82c4628"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R771d30d0416345a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R90a4a9fbf09245c4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T17:49:59.196Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T18:07:55.978Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>88062f7a6e23d78621ee2f69e0c94047babf12437db78098dd47d3bedd6e18e8</x:v>
+        <x:v>5385d4f4cf361a2e56db9b88d4a9952e6d93bf5f83f0834cb083bcdd6684e517</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>fb798ccf47bd62d17275121a5ca1021b3ed9a80358d236bd57d75a7be070b894</x:v>
+        <x:v>d50c68edff009ac84589ad37b15985dac299e304fb4daa2752ebe808d92740fd</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6aa021399ce74992"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R636bc24063de4d88"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d292687eb104057"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c602efceb694708"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde0b57c891514689"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re15a29ba6aee4c4d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rae3ebd355d6d45fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R99963fb4a82c4628"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R771d30d0416345a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R90a4a9fbf09245c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Re44ef7cba2144c74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R9cb14d7bd3e844b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R5e88782b6eb44440"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R234faf9287cf4904"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T18:07:55.978Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T18:15:14.532Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5385d4f4cf361a2e56db9b88d4a9952e6d93bf5f83f0834cb083bcdd6684e517</x:v>
+        <x:v>944ecbe81a903e81a65ffa487f20c3a417603b0749843148bbf77414d42d60b4</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R636bc24063de4d88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbca16ab3b5bc45bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c602efceb694708"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8494739ecd6041f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re15a29ba6aee4c4d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R113888d6606b4e0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Re44ef7cba2144c74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R9cb14d7bd3e844b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R5e88782b6eb44440"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R234faf9287cf4904"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R6f3d58061d6d4c32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R19da67d8c5a241a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Re0975dfbc1134269"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R08e9fed5945341a9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T18:15:14.532Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T22:22:25.930Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>944ecbe81a903e81a65ffa487f20c3a417603b0749843148bbf77414d42d60b4</x:v>
+        <x:v>325f8ef8696abef155a85a11a511a71ee5bbd155d28b2e0bfd11928b39ade4e3</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>d50c68edff009ac84589ad37b15985dac299e304fb4daa2752ebe808d92740fd</x:v>
+        <x:v>75fa53533f9758516132ea54608152663cd0f407a24b0e6a3e030bc743a6ab27</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbca16ab3b5bc45bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98d2ced548dc418e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8494739ecd6041f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01130cd4cd54400e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R113888d6606b4e0f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b77db8a7a7d4c35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R6f3d58061d6d4c32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R19da67d8c5a241a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Re0975dfbc1134269"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R08e9fed5945341a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Ra2b3f5ec1e5d4941"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R718e4a7303ec4943"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R3f6ce23665c5487e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R9cea7c004a5f458c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-24T22:22:25.930Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-25T11:43:35.202Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>325f8ef8696abef155a85a11a511a71ee5bbd155d28b2e0bfd11928b39ade4e3</x:v>
+        <x:v>8794d15eced755667fbb94a78904d0b24ab39e7c75d28fc3bbe150bece4e8ceb</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>75fa53533f9758516132ea54608152663cd0f407a24b0e6a3e030bc743a6ab27</x:v>
+        <x:v>fa54e193a88aab1a463c7e9a9d929aac8295554193f697131ae924624c8c3635</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98d2ced548dc418e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7df4669b380429d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01130cd4cd54400e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R595ed91a3b38487b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b77db8a7a7d4c35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcdd76e311f042f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Ra2b3f5ec1e5d4941"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R718e4a7303ec4943"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R3f6ce23665c5487e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R9cea7c004a5f458c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R23925ef7369843dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rcaf044edf8114111"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R59999c0a5c684f47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rfdd0484eb4184f8f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-25T11:43:35.202Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-25T12:31:42.928Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>8794d15eced755667fbb94a78904d0b24ab39e7c75d28fc3bbe150bece4e8ceb</x:v>
+        <x:v>6638c6d858c0c15d03f1b8c7f8d4371e61b16cbc58edb9c36dd4e72b917f5303</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>fa54e193a88aab1a463c7e9a9d929aac8295554193f697131ae924624c8c3635</x:v>
+        <x:v>8efd0e5d2f1745401819248f5cd349c1ca2995df2b2938bff0ddd27c9679b4c8</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7df4669b380429d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf07988d08a1940b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R595ed91a3b38487b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce51b374bfca47b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcdd76e311f042f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f6228e169874e16"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R23925ef7369843dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rcaf044edf8114111"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R59999c0a5c684f47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rfdd0484eb4184f8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R900983c7345a4d99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R4a1e14609dbd4b98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R789930b090a845d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rc796dfdffac14b1b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-25T12:31:42.928Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-31T15:58:16.965Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>6638c6d858c0c15d03f1b8c7f8d4371e61b16cbc58edb9c36dd4e72b917f5303</x:v>
+        <x:v>7958b4809b6199a78823ea47abdd37329f78f9de03404b0f973483495d74be9e</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>8efd0e5d2f1745401819248f5cd349c1ca2995df2b2938bff0ddd27c9679b4c8</x:v>
+        <x:v>de942b6ea94208f140cd0ec1bb6d7282f467a001cb150dd4c584a870ba9c4c2b</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf07988d08a1940b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4043234bb554411"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce51b374bfca47b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdf2d8a59912487b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f6228e169874e16"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb3e1879597f4f24"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R900983c7345a4d99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R4a1e14609dbd4b98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R789930b090a845d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rc796dfdffac14b1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R9ab25547a5e0426b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R31f11f3e86a64593"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R737a5ae8933c40e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R1c7c721722454963"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-31T15:58:16.965Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-31T16:19:36.678Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>7958b4809b6199a78823ea47abdd37329f78f9de03404b0f973483495d74be9e</x:v>
+        <x:v>3cdbadaba0ffc908418f454ec3a56c6c112739ccae548d5038c524ed0fb572ae</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>de942b6ea94208f140cd0ec1bb6d7282f467a001cb150dd4c584a870ba9c4c2b</x:v>
+        <x:v>19f49808ff7b94351ad8e2bad9b30d5c978e8d5e96c5f164a91146ca0afcd5ac</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4043234bb554411"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc929b65d257c40a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdf2d8a59912487b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R401f3666633549d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb3e1879597f4f24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c03add645fb4342"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R9ab25547a5e0426b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R31f11f3e86a64593"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R737a5ae8933c40e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R1c7c721722454963"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R5a668ebaaf3f46ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rf4bdc539f9fb45a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R1be302cf39664d73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R35b59ae2085b4381"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-31T16:19:36.678Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-11-01T00:50:08.502Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>3cdbadaba0ffc908418f454ec3a56c6c112739ccae548d5038c524ed0fb572ae</x:v>
+        <x:v>b59c831ec1c00c49183c1e83c86ee8d801e0152690935057f3be6f551a8b788b</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>19f49808ff7b94351ad8e2bad9b30d5c978e8d5e96c5f164a91146ca0afcd5ac</x:v>
+        <x:v>2a343075b78e07a39b50033e252aeaec71194df376aa048789dba03e95d6e972</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc929b65d257c40a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff9f76319d70486c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R401f3666633549d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92325619ecaa42e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c03add645fb4342"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2ee2dedb03c4c75"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/decoration/register.xlsx
+++ b/docs/electrical-grid/categories/decoration/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R9ab25547a5e0426b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R31f11f3e86a64593"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R737a5ae8933c40e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R1c7c721722454963"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R0b3ad36bb5b34079"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rd75b09b4f03f480e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R4a6835ae605142e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R943a155bc26e4f4e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-10-31T16:19:36.678Z.</x:v>
+        <x:v>Decoration and furnishings. Seasonal decorative lighting and non-electrical simulator furnishings. Model snapshot: 2026-11-01T01:42:20.339Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>3cdbadaba0ffc908418f454ec3a56c6c112739ccae548d5038c524ed0fb572ae</x:v>
+        <x:v>50118e5af402ff0efaabf2d570ac3f0129d03efc89e10e7eeb51b8d67485750c</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>19f49808ff7b94351ad8e2bad9b30d5c978e8d5e96c5f164a91146ca0afcd5ac</x:v>
+        <x:v>0fb0ba42a427dbbe355fa325c0efcf0641bfb0dae62bd4f360bc65584cfd7d81</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3350,7 +3350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc929b65d257c40a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd567f91d0b543ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3660,7 +3660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R401f3666633549d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8898ff97a05347db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3769,7 +3769,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c03add645fb4342"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9128c0927c214f88"/>
   </x:tableParts>
 </x:worksheet>
 </file>